--- a/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07980844_Hemas_Holdings_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 157 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>5</v>
